--- a/TELEMETRYadcCLOCK/project/Pre Hopper Run Checks.xlsx
+++ b/TELEMETRYadcCLOCK/project/Pre Hopper Run Checks.xlsx
@@ -9,14 +9,13 @@
   <sheets>
     <sheet name="No Zero Net" sheetId="1" r:id="rId1"/>
     <sheet name="Validate no &quot;text&quot; in Datamaps" sheetId="2" r:id="rId2"/>
-    <sheet name="Missing Bio Symbol Files" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -43,12 +42,6 @@
   </si>
   <si>
     <t>Xdatamap1 (datamap.function) missing expected field datamap_function_2</t>
-  </si>
-  <si>
-    <t>Missing Bio Symbol Files</t>
-  </si>
-  <si>
-    <t>No missing bio or symbol files...</t>
   </si>
 </sst>
 </file>
@@ -445,29 +438,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>